--- a/0708/입출력 결선도.xlsx
+++ b/0708/입출력 결선도.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sozx2\OneDrive\바탕 화면\plc_test\0708\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C97575-8FEB-458E-BA88-C3F9C2DB966A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="229">
   <si>
     <t>센서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -247,82 +248,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>m500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>m501</t>
-  </si>
-  <si>
-    <t>m502</t>
-  </si>
-  <si>
-    <t>m503</t>
-  </si>
-  <si>
-    <t>m504</t>
-  </si>
-  <si>
-    <t>m505</t>
-  </si>
-  <si>
-    <t>m506</t>
-  </si>
-  <si>
-    <t>m507</t>
-  </si>
-  <si>
-    <t>m508</t>
-  </si>
-  <si>
-    <t>m509</t>
-  </si>
-  <si>
-    <t>m510</t>
-  </si>
-  <si>
-    <t>m511</t>
-  </si>
-  <si>
-    <t>m600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>m601</t>
-  </si>
-  <si>
-    <t>m602</t>
-  </si>
-  <si>
-    <t>m603</t>
-  </si>
-  <si>
-    <t>m604</t>
-  </si>
-  <si>
-    <t>m605</t>
-  </si>
-  <si>
-    <t>m606</t>
-  </si>
-  <si>
-    <t>m607</t>
-  </si>
-  <si>
-    <t>m608</t>
-  </si>
-  <si>
-    <t>m609</t>
-  </si>
-  <si>
-    <t>blink</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>blink_0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>m101</t>
   </si>
   <si>
@@ -370,18 +295,6 @@
     <t>m406</t>
   </si>
   <si>
-    <t>1~9 초기화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">11~30 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100~ 102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -530,43 +443,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>m700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>m701</t>
-  </si>
-  <si>
-    <t>m702</t>
-  </si>
-  <si>
-    <t>m703</t>
-  </si>
-  <si>
-    <t>m704</t>
-  </si>
-  <si>
-    <t>m705</t>
-  </si>
-  <si>
-    <t>m706</t>
-  </si>
-  <si>
-    <t>m707</t>
-  </si>
-  <si>
-    <t>m708</t>
-  </si>
-  <si>
-    <t>m709</t>
-  </si>
-  <si>
-    <t>m710</t>
-  </si>
-  <si>
-    <t>m711</t>
-  </si>
-  <si>
     <t>공급_전2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -615,14 +491,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>m512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>m513</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>드릴정지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -639,14 +507,357 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>m514</t>
+    <t>m105</t>
+  </si>
+  <si>
+    <t>m106</t>
+  </si>
+  <si>
+    <t>m107</t>
+  </si>
+  <si>
+    <t>m108</t>
+  </si>
+  <si>
+    <t>m109</t>
+  </si>
+  <si>
+    <t>m110</t>
+  </si>
+  <si>
+    <t>m111</t>
+  </si>
+  <si>
+    <t>m112</t>
+  </si>
+  <si>
+    <t>m113</t>
+  </si>
+  <si>
+    <t>m114</t>
+  </si>
+  <si>
+    <t>m115</t>
+  </si>
+  <si>
+    <t>m116</t>
+  </si>
+  <si>
+    <t>m117</t>
+  </si>
+  <si>
+    <t>m200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m201</t>
+  </si>
+  <si>
+    <t>m202</t>
+  </si>
+  <si>
+    <t>m203</t>
+  </si>
+  <si>
+    <t>m204</t>
+  </si>
+  <si>
+    <t>m205</t>
+  </si>
+  <si>
+    <t>m206</t>
+  </si>
+  <si>
+    <t>m207</t>
+  </si>
+  <si>
+    <t>m208</t>
+  </si>
+  <si>
+    <t>m209</t>
+  </si>
+  <si>
+    <t>m210</t>
+  </si>
+  <si>
+    <t>m211</t>
+  </si>
+  <si>
+    <t>m212</t>
+  </si>
+  <si>
+    <t>m213</t>
+  </si>
+  <si>
+    <t>m214</t>
+  </si>
+  <si>
+    <t>m215</t>
+  </si>
+  <si>
+    <t>m216</t>
+  </si>
+  <si>
+    <t>m217</t>
+  </si>
+  <si>
+    <t>m300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m302</t>
+  </si>
+  <si>
+    <t>m303</t>
+  </si>
+  <si>
+    <t>m304</t>
+  </si>
+  <si>
+    <t>m305</t>
+  </si>
+  <si>
+    <t>m306</t>
+  </si>
+  <si>
+    <t>m307</t>
+  </si>
+  <si>
+    <t>m308</t>
+  </si>
+  <si>
+    <t>m309</t>
+  </si>
+  <si>
+    <t>m310</t>
+  </si>
+  <si>
+    <t>m311</t>
+  </si>
+  <si>
+    <t>m312</t>
+  </si>
+  <si>
+    <t>m313</t>
+  </si>
+  <si>
+    <t>m314</t>
+  </si>
+  <si>
+    <t>m315</t>
+  </si>
+  <si>
+    <t>m316</t>
+  </si>
+  <si>
+    <t>m317</t>
+  </si>
+  <si>
+    <t>m400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m407</t>
+  </si>
+  <si>
+    <t>m408</t>
+  </si>
+  <si>
+    <t>m409</t>
+  </si>
+  <si>
+    <t>m410</t>
+  </si>
+  <si>
+    <t>m411</t>
+  </si>
+  <si>
+    <t>m412</t>
+  </si>
+  <si>
+    <t>m413</t>
+  </si>
+  <si>
+    <t>m414</t>
+  </si>
+  <si>
+    <t>m415</t>
+  </si>
+  <si>
+    <t>m416</t>
+  </si>
+  <si>
+    <t>m417</t>
+  </si>
+  <si>
+    <t>m90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m91</t>
+  </si>
+  <si>
+    <t>m92</t>
+  </si>
+  <si>
+    <t>m93</t>
+  </si>
+  <si>
+    <t>m94</t>
+  </si>
+  <si>
+    <t>공급_전3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공급_후3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴_하3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송출_전3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송출_후3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배출_전3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배출_후3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨베이어3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가공드릴3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적색3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황색3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹색3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴상승3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴정지3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴정지2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴상승2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공급_전4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공급_후4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴_하4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송출_전4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송출_후4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배출_전4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배출_후4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨베이어4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가공드릴4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적색4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황색4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹색4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴정지4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴상승4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금속탐지4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비금속탐지4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금속탐지2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비금속탐지2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금속탐지3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비금속탐지3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -664,7 +875,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,8 +900,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -744,21 +973,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -878,7 +1092,94 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -887,125 +1188,143 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1287,8 +1606,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:R32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C3:V45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
@@ -1298,968 +1617,1364 @@
     <col min="7" max="7" width="15.875" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.875" customWidth="1"/>
-    <col min="10" max="10" width="10.125" customWidth="1"/>
-    <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="15.625" customWidth="1"/>
-    <col min="13" max="13" width="8.875" customWidth="1"/>
-    <col min="14" max="15" width="11.25" customWidth="1"/>
+    <col min="10" max="10" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C4" s="33" t="s">
+    <row r="3" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34" t="s">
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="34"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="35" t="s">
+      <c r="H4" s="24"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C5" s="12" t="s">
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="42"/>
+    </row>
+    <row r="5" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C6" s="11" t="s">
+      <c r="I5" s="33"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+    </row>
+    <row r="6" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="8" t="s">
+      <c r="J6" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q6" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C7" s="11" t="s">
+      <c r="L6" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="M6" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="O6" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="P6" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q6" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="R6" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="S6" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+    </row>
+    <row r="7" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="5" t="s">
         <v>54</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="J7" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="O7" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q7" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C8" s="11" t="s">
+      <c r="L7" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="M7" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="O7" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="P7" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="R7" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="S7" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+    </row>
+    <row r="8" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="J8" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="O8" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C9" s="11" t="s">
+      <c r="L8" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="O8" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="P8" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="R8" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="S8" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+    </row>
+    <row r="9" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>130</v>
+      <c r="E9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q9" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C10" s="11" t="s">
+      <c r="L9" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="O9" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="P9" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q9" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="R9" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="S9" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+    </row>
+    <row r="10" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>131</v>
+      <c r="E10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="8" t="s">
+      <c r="J10" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q10" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C11" s="11" t="s">
+      <c r="L10" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="P10" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q10" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="R10" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="S10" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+    </row>
+    <row r="11" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="J11" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="K11" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="3"/>
-      <c r="Q11" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C12" s="11" t="s">
+      <c r="L11" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="M11" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="O11" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+    </row>
+    <row r="12" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" s="8" t="s">
+      <c r="J12" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q12" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C13" s="11" t="s">
+      <c r="L12" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="N12" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="O12" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="P12" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+    </row>
+    <row r="13" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="8" t="s">
+      <c r="I13" s="33"/>
+      <c r="J13" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q13" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="R13" s="8" t="s">
+      <c r="L13" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="M13" s="44" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C14" s="11" t="s">
+      <c r="N13" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="O13" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="P13" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q13" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+    </row>
+    <row r="14" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>135</v>
+      <c r="E14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="K14" s="8" t="s">
+      <c r="I14" s="33"/>
+      <c r="J14" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="L14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="15" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C15" s="11" t="s">
+      <c r="L14" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="N14" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="O14" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="P14" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q14" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
+    </row>
+    <row r="15" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C15" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>136</v>
+      <c r="E15" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="I15" s="33"/>
+      <c r="J15" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="L15" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="O15" s="3"/>
-      <c r="Q15" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="3:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="11" t="s">
+      <c r="L15" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="N15" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="O15" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q15" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="R15" s="36"/>
+      <c r="S15" s="36"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="36"/>
+    </row>
+    <row r="16" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C16" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>137</v>
+      <c r="E16" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="8" t="s">
+      <c r="I16" s="33"/>
+      <c r="J16" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="K16" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="M16" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="N16" s="15" t="s">
+      <c r="L16" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="N16" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="O16" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q16" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="R16" s="36"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="36"/>
+    </row>
+    <row r="17" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="35"/>
+      <c r="J17" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="N17" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="O17" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="P17" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q17" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="36"/>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="J18" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="K18" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="L18" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="N18" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="O18" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="P18" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q18" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="36"/>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="K19" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="L19" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="M19" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="N19" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="O19" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="P19" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q19" s="44" t="s">
+        <v>222</v>
+      </c>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="36"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H20" s="28"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="K20" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="L20" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="N20" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="O20" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="P20" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q20" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H21" s="28"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="L21" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="M21" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="N21" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="O21" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="P21" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q21" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="R21" s="36"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="36"/>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H22" s="28"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="K22" s="44"/>
+      <c r="L22" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="M22" s="44"/>
+      <c r="N22" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="O22" s="44"/>
+      <c r="P22" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+    </row>
+    <row r="23" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" s="45"/>
+      <c r="L23" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="M23" s="45"/>
+      <c r="N23" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="O23" s="45"/>
+      <c r="P23" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
+      <c r="U23" s="43"/>
+      <c r="V23" s="43"/>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H24" s="28"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="39"/>
+      <c r="V24" s="39"/>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H26" s="28"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H27" s="28"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H28" s="28"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H29" s="28"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H30" s="28"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="H31" s="28"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+    </row>
+    <row r="32" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H32" s="30"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+    </row>
+    <row r="33" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C33" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="13">
+        <v>8</v>
+      </c>
+      <c r="E33" s="13">
+        <v>4</v>
+      </c>
+      <c r="F33" s="13">
+        <v>2</v>
+      </c>
+      <c r="G33" s="13">
+        <v>1</v>
+      </c>
+      <c r="H33" s="26">
+        <v>8</v>
+      </c>
+      <c r="I33" s="26">
+        <v>4</v>
+      </c>
+      <c r="J33" s="26">
+        <v>2</v>
+      </c>
+      <c r="K33" s="26">
+        <v>1</v>
+      </c>
+      <c r="L33" s="27">
+        <v>8</v>
+      </c>
+      <c r="M33" s="13">
+        <v>4</v>
+      </c>
+      <c r="N33" s="13">
+        <v>2</v>
+      </c>
+      <c r="O33" s="13">
+        <v>1</v>
+      </c>
+      <c r="P33" s="20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C34" s="25"/>
+      <c r="D34" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K34" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="Q16" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="3:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="N17" s="15" t="s">
+      <c r="L34" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="O17" s="6"/>
-      <c r="Q17" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-    </row>
-    <row r="19" spans="3:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="K19" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C20" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="22">
+      <c r="M34" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="N34" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="P34" s="21"/>
+    </row>
+    <row r="35" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C35" s="25"/>
+      <c r="D35" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="N35" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="O35" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="P35" s="22"/>
+    </row>
+    <row r="36" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C36" s="14">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="11">
+        <v>1</v>
+      </c>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="15">
         <v>8</v>
       </c>
-      <c r="E20" s="22">
+    </row>
+    <row r="37" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C37" s="14">
+        <v>2</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="11">
+        <v>1</v>
+      </c>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11">
+        <v>1</v>
+      </c>
+      <c r="P37" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C38" s="14">
+        <v>3</v>
+      </c>
+      <c r="D38" s="11">
+        <v>1</v>
+      </c>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="11">
+        <v>1</v>
+      </c>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11">
+        <v>1</v>
+      </c>
+      <c r="P38" s="15">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="39" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C39" s="14">
         <v>4</v>
       </c>
-      <c r="F20" s="22">
-        <v>2</v>
-      </c>
-      <c r="G20" s="22">
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="11">
         <v>1</v>
       </c>
-      <c r="H20" s="23">
+      <c r="M39" s="11"/>
+      <c r="N39" s="11">
+        <v>1</v>
+      </c>
+      <c r="O39" s="11"/>
+      <c r="P39" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C40" s="14">
+        <v>5</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11">
+        <v>1</v>
+      </c>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="11">
+        <v>1</v>
+      </c>
+      <c r="M40" s="11">
+        <v>1</v>
+      </c>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="15">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="41" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C41" s="14">
+        <v>6</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12">
+        <v>1</v>
+      </c>
+      <c r="K41" s="12"/>
+      <c r="L41" s="11">
+        <v>1</v>
+      </c>
+      <c r="M41" s="11">
+        <v>1</v>
+      </c>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C42" s="14">
+        <v>7</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11">
+        <v>1</v>
+      </c>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12">
+        <v>1</v>
+      </c>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="11">
+        <v>1</v>
+      </c>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="15">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C43" s="14">
         <v>8</v>
       </c>
-      <c r="I20" s="23">
-        <v>4</v>
-      </c>
-      <c r="J20" s="23">
-        <v>2</v>
-      </c>
-      <c r="K20" s="23">
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12">
         <v>1</v>
       </c>
-      <c r="L20" s="22">
-        <v>8</v>
-      </c>
-      <c r="M20" s="22">
-        <v>4</v>
-      </c>
-      <c r="N20" s="22">
-        <v>2</v>
-      </c>
-      <c r="O20" s="22">
-        <v>1</v>
-      </c>
-      <c r="P20" s="30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C21" s="37"/>
-      <c r="D21" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="H21" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="I21" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="J21" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="L21" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="M21" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="N21" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="O21" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="P21" s="31"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C22" s="37"/>
-      <c r="D22" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="I22" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="J22" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="K22" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="L22" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="M22" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="N22" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P22" s="32"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C23" s="24">
-        <v>1</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="20">
-        <v>1</v>
-      </c>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C24" s="24">
-        <v>2</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="20">
-        <v>1</v>
-      </c>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20">
-        <v>1</v>
-      </c>
-      <c r="P24" s="25">
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C44" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C25" s="24">
-        <v>3</v>
-      </c>
-      <c r="D25" s="20">
-        <v>1</v>
-      </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="20">
-        <v>1</v>
-      </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20">
-        <v>1</v>
-      </c>
-      <c r="P25" s="25">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C26" s="24">
-        <v>4</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="20">
-        <v>1</v>
-      </c>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20">
-        <v>1</v>
-      </c>
-      <c r="O26" s="20"/>
-      <c r="P26" s="25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="15"/>
+    </row>
+    <row r="45" spans="3:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C45" s="16">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C27" s="24">
-        <v>5</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20">
-        <v>1</v>
-      </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="20">
-        <v>1</v>
-      </c>
-      <c r="M27" s="20">
-        <v>1</v>
-      </c>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="25">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C28" s="24">
-        <v>6</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20">
-        <v>1</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21">
-        <v>1</v>
-      </c>
-      <c r="K28" s="21"/>
-      <c r="L28" s="20">
-        <v>1</v>
-      </c>
-      <c r="M28" s="20">
-        <v>1</v>
-      </c>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C29" s="24">
-        <v>7</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20">
-        <v>1</v>
-      </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21">
-        <v>1</v>
-      </c>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="20">
-        <v>1</v>
-      </c>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="25">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C30" s="24">
-        <v>8</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21">
-        <v>1</v>
-      </c>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C31" s="24">
-        <v>9</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="25"/>
-    </row>
-    <row r="32" spans="3:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="26">
-        <v>10</v>
-      </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="29"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="P20:P22"/>
+    <mergeCell ref="P33:P35"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="J4:V4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
